--- a/output/rf_dgp2extranoise_output.xlsx
+++ b/output/rf_dgp2extranoise_output.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5cac48941448979/Bureaublad/msc_thesis/thesis_code/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="11_42CED8000997A4AF3E4C218E24D62AEDE9E2BF34" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{84454AF6-B4B0-40FF-862D-3B418DFD4E87}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED800A28765B926DD209FC49623EDE9E2BF28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05127B3C-4417-44BD-A137-FE2909269BCE}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misclassification_rates" sheetId="1" r:id="rId1"/>
@@ -378,52 +378,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.28299999999999997</v>
+        <v>0.29199999999999998</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.28399999999999997</v>
+        <v>0.29899999999999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.28599999999999998</v>
+        <v>0.29899999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.30199999999999999</v>
+        <v>0.27200000000000002</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.27</v>
+        <v>0.26300000000000001</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.29699999999999999</v>
+        <v>0.26100000000000001</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.254</v>
+        <v>0.26400000000000001</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.308</v>
+        <v>0.28699999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.29599999999999999</v>
+        <v>0.23499999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.26900000000000002</v>
+        <v>0.27100000000000002</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -432,7 +432,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.28489999999999999</v>
+        <v>0.27429999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -441,7 +441,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>1.6769350348511146E-2</v>
+        <v>2.0182775935050266E-2</v>
       </c>
     </row>
   </sheetData>
@@ -457,52 +457,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.43437051999999998</v>
+        <v>0.40712691200000001</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.42699003200000002</v>
+        <v>0.40640178399999999</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.39645167999999997</v>
+        <v>0.44478903199999997</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.39440505599999998</v>
+        <v>0.39027092800000002</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.41989995200000002</v>
+        <v>0.39397241599999999</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.43999849600000002</v>
+        <v>0.37907269599999999</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.42255683199999999</v>
+        <v>0.383585024</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.42718928</v>
+        <v>0.403431072</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.39991045600000003</v>
+        <v>0.34126681599999997</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.427626848</v>
+        <v>0.39433830399999997</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -511,7 +511,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.41893991520000001</v>
+        <v>0.39442549840000002</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>1.6240178929593913E-2</v>
+        <v>2.6074437204413416E-2</v>
       </c>
     </row>
   </sheetData>

--- a/output/rf_dgp2extranoise_output.xlsx
+++ b/output/rf_dgp2extranoise_output.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f5cac48941448979/Bureaublad/msc_thesis/thesis_code/output/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED800A28765B926DD209FC49623EDE9E2BF28" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{05127B3C-4417-44BD-A137-FE2909269BCE}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="11_42CED8005E0FE1D2C88FA7DD04D431EDE9E2BF2B" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2BFB869-0088-4514-B296-E1BC591DFA38}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="misclassification_rates" sheetId="1" r:id="rId1"/>
@@ -378,52 +378,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.29199999999999998</v>
+        <v>0.30499999999999999</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.29899999999999999</v>
+        <v>0.318</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.29899999999999999</v>
+        <v>0.28599999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.27200000000000002</v>
+        <v>0.29299999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.26300000000000001</v>
+        <v>0.316</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.26100000000000001</v>
+        <v>0.28000000000000003</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.26400000000000001</v>
+        <v>0.27</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.28699999999999998</v>
+        <v>0.29399999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.23499999999999999</v>
+        <v>0.26900000000000002</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.27100000000000002</v>
+        <v>0.34200000000000003</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -432,7 +432,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.27429999999999999</v>
+        <v>0.29730000000000001</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -441,7 +441,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>2.0182775935050266E-2</v>
+        <v>2.3185483964469379E-2</v>
       </c>
     </row>
   </sheetData>
@@ -457,52 +457,52 @@
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1">
-        <v>0.40712691200000001</v>
+        <v>0.46305243200000001</v>
       </c>
     </row>
     <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2">
-        <v>0.40640178399999999</v>
+        <v>0.46585312000000001</v>
       </c>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3">
-        <v>0.44478903199999997</v>
+        <v>0.43480832800000002</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4">
-        <v>0.39027092800000002</v>
+        <v>0.41887883199999998</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5">
-        <v>0.39397241599999999</v>
+        <v>0.43620917599999998</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>0.37907269599999999</v>
+        <v>0.453604016</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7">
-        <v>0.383585024</v>
+        <v>0.40941618400000002</v>
       </c>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8">
-        <v>0.403431072</v>
+        <v>0.43110933600000001</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9">
-        <v>0.34126681599999997</v>
+        <v>0.45553541600000003</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10">
-        <v>0.39433830399999997</v>
+        <v>0.45490125599999998</v>
       </c>
     </row>
     <row r="12" spans="1:2" x14ac:dyDescent="0.3">
@@ -511,7 +511,7 @@
       </c>
       <c r="B12">
         <f>AVERAGE(A1:A10)</f>
-        <v>0.39442549840000002</v>
+        <v>0.44233680959999999</v>
       </c>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.3">
@@ -520,7 +520,7 @@
       </c>
       <c r="B13">
         <f>_xlfn.STDEV.S(A1:A10)</f>
-        <v>2.6074437204413416E-2</v>
+        <v>1.9135478177409064E-2</v>
       </c>
     </row>
   </sheetData>
